--- a/rwa_tokenization_model/outputs/reports/model_results.xlsx
+++ b/rwa_tokenization_model/outputs/reports/model_results.xlsx
@@ -547,28 +547,28 @@
         <v>0.0369</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04</v>
+        <v>0.0369</v>
       </c>
       <c r="J2" t="n">
-        <v>0.003099999999999999</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06300926205232323</v>
+        <v>0.0586893867695342</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06209153848831139</v>
+        <v>0.05627432475897674</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="N2" t="n">
-        <v>0.09806683953051196</v>
+        <v>0.08871480085063695</v>
       </c>
       <c r="O2" t="n">
-        <v>0.09801887868911499</v>
+        <v>0.08862309071923274</v>
       </c>
       <c r="P2" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="Q2" t="n">
         <v>1.519129833317511</v>
@@ -663,10 +663,10 @@
         <v>0.9520000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="H2" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="I2" t="n">
         <v>0.0003140607326432843</v>
@@ -694,10 +694,10 @@
         <v>0.9549999999999998</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="H3" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="I3" t="n">
         <v>0.0007851518316086548</v>
@@ -725,10 +725,10 @@
         <v>0.958</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="I4" t="n">
         <v>0.001256242930573803</v>
@@ -830,13 +830,13 @@
         <v>1.447290000000002</v>
       </c>
       <c r="H2" t="n">
-        <v>0.04</v>
+        <v>0.0369</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="J2" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="K2" t="n">
         <v>0.0007851518316086548</v>
@@ -873,7 +873,7 @@
         <v>-0.0007245186031672318</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.786382215549555e-05</v>
+        <v>-2.751303942125083e-05</v>
       </c>
       <c r="K3" t="n">
         <v>0.001046869108811466</v>
@@ -910,7 +910,7 @@
         <v>0.0009660248042229758</v>
       </c>
       <c r="J4" t="n">
-        <v>5.048509620733665e-05</v>
+        <v>3.668405256168628e-05</v>
       </c>
       <c r="K4" t="n">
         <v>0.001570303663217087</v>
@@ -947,7 +947,7 @@
         <v>0.002415062010557453</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0001262127405183416</v>
+        <v>9.171013140420181e-05</v>
       </c>
       <c r="K5" t="n">
         <v>0.001439445024615793</v>
@@ -1030,10 +1030,10 @@
         <v>0.9520000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G2" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="H2" t="n">
         <v>0.0003140607326432843</v>
@@ -1063,7 +1063,7 @@
         <v>-0.0007245186031672318</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.786382215549555e-05</v>
+        <v>-2.751303942125083e-05</v>
       </c>
       <c r="H3" t="n">
         <v>0.000418747643524453</v>
@@ -1093,7 +1093,7 @@
         <v>0.0009660248042229758</v>
       </c>
       <c r="G4" t="n">
-        <v>5.048509620733665e-05</v>
+        <v>3.668405256168628e-05</v>
       </c>
       <c r="H4" t="n">
         <v>0.0006281214652870126</v>
@@ -1123,7 +1123,7 @@
         <v>0.002415062010557453</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0001262127405183416</v>
+        <v>9.171013140420181e-05</v>
       </c>
       <c r="H5" t="n">
         <v>0.0005757780098460952</v>
@@ -1150,10 +1150,10 @@
         <v>0.9549999999999998</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="H6" t="n">
         <v>0.0007851518316086548</v>
@@ -1183,7 +1183,7 @@
         <v>-0.0007245186031672318</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.786382215549555e-05</v>
+        <v>-2.751303942125083e-05</v>
       </c>
       <c r="H7" t="n">
         <v>0.001046869108811466</v>
@@ -1213,7 +1213,7 @@
         <v>0.0009660248042229758</v>
       </c>
       <c r="G8" t="n">
-        <v>5.048509620733665e-05</v>
+        <v>3.668405256168628e-05</v>
       </c>
       <c r="H8" t="n">
         <v>0.001570303663217087</v>
@@ -1243,7 +1243,7 @@
         <v>0.002415062010557453</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0001262127405183416</v>
+        <v>9.171013140420181e-05</v>
       </c>
       <c r="H9" t="n">
         <v>0.001439445024615793</v>
@@ -1270,10 +1270,10 @@
         <v>0.958</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="H10" t="n">
         <v>0.001256242930573803</v>
@@ -1303,7 +1303,7 @@
         <v>-0.0007245186031672318</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.786382215549555e-05</v>
+        <v>-2.751303942125083e-05</v>
       </c>
       <c r="H11" t="n">
         <v>0.001674990574098256</v>
@@ -1333,7 +1333,7 @@
         <v>0.0009660248042229758</v>
       </c>
       <c r="G12" t="n">
-        <v>5.048509620733665e-05</v>
+        <v>3.668405256168628e-05</v>
       </c>
       <c r="H12" t="n">
         <v>0.002512485861147606</v>
@@ -1363,7 +1363,7 @@
         <v>0.002415062010557453</v>
       </c>
       <c r="G13" t="n">
-        <v>0.0001262127405183416</v>
+        <v>9.171013140420181e-05</v>
       </c>
       <c r="H13" t="n">
         <v>0.002303112039385269</v>
@@ -1402,7 +1402,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
     </row>
     <row r="3">
@@ -1412,7 +1412,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
     </row>
   </sheetData>
@@ -1640,22 +1640,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.04271460273356724</v>
+        <v>0.04242885608772652</v>
       </c>
       <c r="C4" t="n">
         <v>0.04242206756746053</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002337461043274617</v>
+        <v>0.002742188076504325</v>
       </c>
       <c r="E4" t="n">
-        <v>0.04</v>
+        <v>0.03594926318178243</v>
       </c>
       <c r="F4" t="n">
         <v>0.04883540412435572</v>
       </c>
       <c r="G4" t="n">
-        <v>0.04</v>
+        <v>0.03792034294811684</v>
       </c>
       <c r="H4" t="n">
         <v>0.04695103755733782</v>
@@ -1668,22 +1668,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0003934632231069024</v>
+        <v>0.0002554440493040761</v>
       </c>
       <c r="C5" t="n">
         <v>0.0002521651098236141</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001129022673354106</v>
+        <v>0.001324510849873844</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.00287427968490056</v>
       </c>
       <c r="F5" t="n">
         <v>0.003349886205719008</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.001922223712210014</v>
       </c>
       <c r="H5" t="n">
         <v>0.002439713783725098</v>
@@ -1696,25 +1696,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.056264868745347e-05</v>
+        <v>9.700292259865042e-06</v>
       </c>
       <c r="C6" t="n">
-        <v>1.317831568499461e-05</v>
+        <v>9.575777042733491e-06</v>
       </c>
       <c r="D6" t="n">
-        <v>5.900347282530876e-05</v>
+        <v>5.029728576624883e-05</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-0.000109148571110107</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0001750672722274221</v>
+        <v>0.0001272093647171763</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-7.299497423436454e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0001275010585145411</v>
+        <v>9.264626362220568e-05</v>
       </c>
     </row>
     <row r="7">
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -2199,10 +2199,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="F10" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -2490,10 +2490,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0009177235640118325</v>
+        <v>0.002415062010557453</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2522,10 +2522,10 @@
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>4.796084139696566e-05</v>
+        <v>9.171013140420181e-05</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2647,13 +2647,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002898074412668948</v>
       </c>
       <c r="F24" t="n">
         <v>0.0009660248042229896</v>
       </c>
       <c r="G24" t="n">
-        <v>0.001883748368234822</v>
+        <v>0.003864099216891938</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2679,13 +2679,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-0.0001100521576850449</v>
       </c>
       <c r="F25" t="n">
-        <v>5.048509620733665e-05</v>
+        <v>3.668405256168628e-05</v>
       </c>
       <c r="G25" t="n">
-        <v>9.844593760430231e-05</v>
+        <v>0.0001467362102467312</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -2839,10 +2839,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.796084139696566e-05</v>
+        <v>-9.171013140420181e-05</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -2892,10 +2892,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2400</v>
+        <v>3330.75</v>
       </c>
       <c r="C32" t="n">
-        <v>4000</v>
+        <v>5551.25</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -2924,10 +2924,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2400</v>
+        <v>3330.75</v>
       </c>
       <c r="C33" t="n">
-        <v>4000</v>
+        <v>5551.25</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2400</v>
+        <v>3330.75</v>
       </c>
       <c r="C34" t="n">
-        <v>4000</v>
+        <v>5551.25</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.0009177235640118325</v>
+        <v>-0.002415062010557453</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2400</v>
+        <v>3330.75</v>
       </c>
       <c r="C35" t="n">
-        <v>4000</v>
+        <v>5551.25</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -2999,13 +2999,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-6.331655973589034e-05</v>
+        <v>-0.0001214007377951937</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.859956205166937e-05</v>
+        <v>-7.368838814514334e-05</v>
       </c>
       <c r="G35" t="n">
-        <v>2.471699768422098e-05</v>
+        <v>4.771234965005033e-05</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2400</v>
+        <v>3330.75</v>
       </c>
       <c r="C36" t="n">
-        <v>4000</v>
+        <v>5551.25</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3200</v>
+        <v>4441</v>
       </c>
     </row>
     <row r="15">
@@ -3208,7 +3208,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.04</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="16">
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.2</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="17">
@@ -3228,7 +3228,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.05</v>
+        <v>0.0423</v>
       </c>
     </row>
     <row r="18">
@@ -3238,7 +3238,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.1</v>
+        <v>0.08989999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -3258,7 +3258,7 @@
         </is>
       </c>
       <c r="B20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -3268,7 +3268,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.04</v>
+        <v>0.0446</v>
       </c>
     </row>
     <row r="22">
